--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C2C9FD-4D6F-4FD3-9058-D4EDB133E7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAC725D-E30B-4554-908C-734945BE27AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -158,52 +158,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>杨大使所患的是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>气不固之症，要注意修养，最近是遇到什么事受了惊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>您听说沈师爷的事了吗？</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -396,6 +350,69 @@
   </si>
   <si>
     <t>017_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>大使所患的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>肾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>气不固之症，要注意休养，最近是遇到什么事受了惊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>？</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -536,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -586,6 +603,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -939,7 +959,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -956,7 +976,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1098,8 +1118,8 @@
       <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>34</v>
+      <c r="H2" s="19" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1121,7 +1141,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1141,7 +1161,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1163,7 +1183,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1183,7 +1203,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1205,7 +1225,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1225,7 +1245,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAC725D-E30B-4554-908C-734945BE27AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80058AE6-4C9D-417A-87B5-5C932BC18B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -68,10 +68,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>right</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -228,9 +224,40 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>他</t>
-    </r>
+    <t>......</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>017_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -239,7 +266,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>们</t>
+      <t>杨</t>
     </r>
     <r>
       <rPr>
@@ -249,7 +276,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>开始</t>
+      <t>大使所患的是</t>
     </r>
     <r>
       <rPr>
@@ -259,7 +286,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>灭</t>
+      <t>肾</t>
     </r>
     <r>
       <rPr>
@@ -269,6 +296,76 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>气不固之症，要注意休养，最近是遇到什么事受了惊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>他</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>灭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>口了</t>
     </r>
     <r>
@@ -299,7 +396,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>该轮到...</t>
+      <t>该轮到我了...</t>
     </r>
     <rPh sb="0" eb="1">
       <t>ホカ</t>
@@ -316,103 +413,6 @@
     <rPh sb="6" eb="7">
       <t>ハジメ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>......</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>017_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>大使所患的是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>气不固之症，要注意休养，最近是遇到什么事受了惊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>？</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -912,71 +912,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="K1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1091,10 +1091,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>5</v>
@@ -1108,18 +1108,18 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1130,18 +1130,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1152,16 +1152,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1172,18 +1172,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1194,16 +1194,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1214,18 +1214,18 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1236,16 +1236,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80058AE6-4C9D-417A-87B5-5C932BC18B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB2A1FC-AA73-4726-8686-C2C1A68C3C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -413,6 +413,10 @@
     <rPh sb="6" eb="7">
       <t>ハジメ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>这一批药材入库验收、各地调拨都是我经的手，多少药、什么成色、送到哪里，账上都有我的画押。他们想把这笔账做干净，就不会留我这个活口。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -553,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -605,6 +609,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1236,29 +1243,39 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>37</v>
+      <c r="H8" s="20" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
@@ -1268,7 +1285,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB2A1FC-AA73-4726-8686-C2C1A68C3C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB5B500-A0E0-4606-A60C-EA9044ECBE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>LineIndex</t>
   </si>
@@ -76,70 +62,20 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
     <t>018治疗成功</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
   </si>
   <si>
     <t>李东璧</t>
@@ -419,16 +355,104 @@
     <t>这一批药材入库验收、各地调拨都是我经的手，多少药、什么成色、送到哪里，账上都有我的画押。他们想把这笔账做干净，就不会留我这个活口。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -442,7 +466,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -463,20 +487,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -497,8 +513,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,20 +551,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -557,7 +597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -583,24 +623,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -613,9 +642,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -893,174 +950,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="23" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="23" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="M2" s="24"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="T2" s="25"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="13"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8" ht="18.75">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8" ht="18.75">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8" ht="18.75">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{789810FA-A484-41A7-9D1C-4243E6A56B58}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{D202E7AC-F6BA-40BA-B87C-A6510A6AA067}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{484CCC85-9243-4BA6-BA82-AF355ABC38D7}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{3AE591B1-5455-4FDF-9860-0FFD0DBC6198}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{6A948554-BFE8-466E-88AE-23FD9AF62C7C}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1068,216 +1152,216 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1285,7 +1369,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="20"/>
+      <c r="H10" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB5B500-A0E0-4606-A60C-EA9044ECBE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BAC5DA-241E-474F-961C-FB702C85D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20100" yWindow="3720" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>LineIndex</t>
   </si>
@@ -443,6 +454,10 @@
   <si>
     <t>cured</t>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -452,7 +467,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -466,7 +481,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -487,7 +502,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -597,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -670,9 +685,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -951,25 +969,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>29</v>
       </c>
@@ -1031,7 +1049,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -1071,56 +1089,56 @@
       <c r="L3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:20" ht="18.75">
+    <row r="4" spans="1:20">
       <c r="C4" s="9"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:20" ht="18.75">
+    <row r="5" spans="1:20">
       <c r="C5" s="9"/>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:20" ht="18.75">
+    <row r="6" spans="1:20">
       <c r="C6" s="9"/>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:20" ht="18.75">
+    <row r="7" spans="1:20">
       <c r="C7" s="9"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:20" ht="18.75">
+    <row r="8" spans="1:20">
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:20" ht="18.75">
+    <row r="9" spans="1:20">
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:20" ht="18.75">
+    <row r="10" spans="1:20">
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:20" ht="18.75">
+    <row r="11" spans="1:20">
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:20" ht="18.75">
+    <row r="12" spans="1:20">
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:20" ht="18.75">
+    <row r="13" spans="1:20">
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:20" ht="18.75">
+    <row r="14" spans="1:20">
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:20" ht="18.75">
+    <row r="15" spans="1:20">
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:20" ht="18.75">
+    <row r="16" spans="1:20">
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="11"/>
     </row>
     <row r="20" spans="8:8">
@@ -1151,21 +1169,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1190,8 +1208,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1212,8 +1233,9 @@
       <c r="H2" s="14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1234,8 +1256,9 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1254,8 +1277,9 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1276,8 +1300,9 @@
       <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1296,8 +1321,9 @@
       <c r="H6" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1318,8 +1344,9 @@
       <c r="H7" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1340,8 +1367,9 @@
       <c r="H8" s="15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1360,8 +1388,9 @@
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1370,6 +1399,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="15"/>
+      <c r="I10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/017_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/017_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BAC5DA-241E-474F-961C-FB702C85D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC89C5F-C478-4B1F-9115-C92A5D894A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20100" yWindow="3720" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -85,10 +85,6 @@
     <t>current_scene</t>
   </si>
   <si>
-    <t>018治疗成功</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -457,6 +453,32 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>017治</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -989,58 +1011,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>10</v>
@@ -1051,10 +1073,10 @@
     </row>
     <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -1064,10 +1086,10 @@
       <c r="H2" s="14"/>
       <c r="I2" s="24"/>
       <c r="J2" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>12</v>
@@ -1209,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1220,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
@@ -1231,7 +1253,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1243,18 +1265,18 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1266,16 +1288,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1287,18 +1309,18 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1310,16 +1332,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1331,18 +1353,18 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -1354,18 +1376,18 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -1377,16 +1399,16 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" s="3"/>
     </row>
